--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7721" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7721" uniqueCount="1019">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
   </si>
   <si>
     <t xml:space="preserve">
- - Cette entrée de type substanceAdministration permet de décrire un traitement prescrit avec notamment le médicament, le mode d’administration, la quantité, la durée et la fréquence d'administration.</t>
+ - FrMedicationRequestDocument permet de décrire un traitement prescrit avec notamment le médicament, le mode d’administration, la quantité, la durée et la fréquence d'administration.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -392,7 +392,7 @@
 </t>
   </si>
   <si>
-    <t>Partie narrative de l’entrée</t>
+    <t>Partie narrative</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -470,10 +470,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Précondition de l'administration</t>
-  </si>
-  <si>
-    <t>Lien vers la description narrative des conditions préalables dans le document CDA.</t>
+    <t>Extension - Fr Précondition de l'administration</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer le lien vers la description narrative des conditions préalables dans le document.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -547,7 +547,7 @@
     <t>identifierEntree</t>
   </si>
   <si>
-    <t>Identifiant de l'entrée</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:referencePrescription</t>
@@ -562,7 +562,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Statut de l’entrée</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -1598,7 +1598,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-condition|Observation)
 </t>
   </si>
   <si>
@@ -1627,7 +1627,7 @@
     <t>renouvellement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-renouvellement)
 </t>
   </si>
   <si>
@@ -1640,6 +1640,10 @@
     <t>ald</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-en-rapport-avec-ald)
+</t>
+  </si>
+  <si>
     <t>En rapport avec une Affection Longue Durée (ALD)</t>
   </si>
   <si>
@@ -1649,6 +1653,10 @@
     <t>accidentTravail</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-en-rapport-avec-accident-travail)
+</t>
+  </si>
+  <si>
     <t>En rapport avec accident travail</t>
   </si>
   <si>
@@ -1658,6 +1666,10 @@
     <t>prevention</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-en-rapport-avec-la-prevention)
+</t>
+  </si>
+  <si>
     <t>En rapport avec la prévention</t>
   </si>
   <si>
@@ -1667,6 +1679,10 @@
     <t>nonRemboursable</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-non-remboursable)
+</t>
+  </si>
+  <si>
     <t>Non remboursable</t>
   </si>
   <si>
@@ -1674,6 +1690,10 @@
   </si>
   <si>
     <t>horsAMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-hors-nomenclature)
+</t>
   </si>
   <si>
     <t>Hors AMM</t>
@@ -2852,10 +2872,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Instructions au dispensateur</t>
-  </si>
-  <si>
-    <t>Instructions au dispensateur : par exemple pour indiquer que le traitement doit être étiqueté dans une langue étrangère, etc …</t>
+    <t>Extension - Fr Instructions au dispensateur</t>
+  </si>
+  <si>
+    <t>Extension pour représenter les instructions au dispensateur : par exemple pour indiquer que le traitement doit être étiqueté dans une langue étrangère, etc …</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -15416,10 +15436,10 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>509</v>
@@ -15507,13 +15527,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>506</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>81</v>
@@ -15535,10 +15555,10 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>509</v>
@@ -15626,13 +15646,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>506</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>81</v>
@@ -15654,10 +15674,10 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>509</v>
@@ -15745,13 +15765,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>506</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>81</v>
@@ -15773,10 +15793,10 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>509</v>
@@ -15864,13 +15884,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>506</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>81</v>
@@ -15892,10 +15912,10 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="M107" t="s" s="2">
         <v>509</v>
@@ -15983,10 +16003,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16009,13 +16029,13 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16066,7 +16086,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -16081,13 +16101,13 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
@@ -16098,10 +16118,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16127,10 +16147,10 @@
         <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16181,7 +16201,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -16202,7 +16222,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -16213,10 +16233,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16239,13 +16259,13 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16296,7 +16316,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -16311,13 +16331,13 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
@@ -16328,10 +16348,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16357,14 +16377,14 @@
         <v>157</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -16413,7 +16433,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -16428,13 +16448,13 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
@@ -16445,10 +16465,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16474,13 +16494,13 @@
         <v>186</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16509,28 +16529,28 @@
         <v>190</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="Z112" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -16551,7 +16571,7 @@
         <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
@@ -16562,10 +16582,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16588,13 +16608,13 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16645,7 +16665,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -16660,13 +16680,13 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -16677,10 +16697,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16703,13 +16723,13 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16760,7 +16780,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16775,13 +16795,13 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -16792,10 +16812,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16818,16 +16838,16 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16877,7 +16897,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16892,13 +16912,13 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16909,10 +16929,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17024,10 +17044,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17141,14 +17161,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -17170,10 +17190,10 @@
         <v>135</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>152</v>
@@ -17228,7 +17248,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -17260,10 +17280,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17286,17 +17306,17 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -17345,7 +17365,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -17366,21 +17386,21 @@
         <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17406,14 +17426,14 @@
         <v>214</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -17462,7 +17482,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17483,21 +17503,21 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17523,16 +17543,16 @@
         <v>186</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -17560,10 +17580,10 @@
         <v>190</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -17581,7 +17601,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17602,21 +17622,21 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17728,10 +17748,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17845,10 +17865,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17964,10 +17984,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17993,7 +18013,7 @@
         <v>214</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>278</v>
@@ -18083,10 +18103,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18112,10 +18132,10 @@
         <v>214</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -18166,7 +18186,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -18187,21 +18207,21 @@
         <v>81</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18224,19 +18244,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -18285,7 +18305,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -18306,7 +18326,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -18317,10 +18337,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18432,10 +18452,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18549,14 +18569,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18578,10 +18598,10 @@
         <v>135</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>152</v>
@@ -18636,7 +18656,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -18668,10 +18688,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18697,14 +18717,14 @@
         <v>367</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -18753,7 +18773,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18774,7 +18794,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18785,10 +18805,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18811,17 +18831,17 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18870,7 +18890,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18882,7 +18902,7 @@
         <v>81</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>81</v>
@@ -18891,7 +18911,7 @@
         <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>81</v>
@@ -18902,10 +18922,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19017,10 +19037,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19134,10 +19154,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19160,13 +19180,13 @@
         <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19205,7 +19225,7 @@
         <v>81</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AC135" s="2"/>
       <c r="AD135" t="s" s="2">
@@ -19215,7 +19235,7 @@
         <v>139</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -19236,7 +19256,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -19247,13 +19267,13 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>81</v>
@@ -19275,13 +19295,13 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -19332,7 +19352,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -19353,7 +19373,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -19364,10 +19384,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19479,10 +19499,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19596,10 +19616,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19625,13 +19645,13 @@
         <v>367</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19681,7 +19701,7 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19690,7 +19710,7 @@
         <v>90</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>102</v>
@@ -19702,21 +19722,21 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19742,20 +19762,20 @@
         <v>367</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q140" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="R140" t="s" s="2">
         <v>81</v>
@@ -19800,7 +19820,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19809,7 +19829,7 @@
         <v>90</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>102</v>
@@ -19821,21 +19841,21 @@
         <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19858,19 +19878,19 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -19919,7 +19939,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19940,7 +19960,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -19951,10 +19971,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19977,13 +19997,13 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -20034,7 +20054,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -20055,7 +20075,7 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
@@ -20066,10 +20086,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20092,19 +20112,19 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -20153,7 +20173,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -20174,7 +20194,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -20185,10 +20205,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20211,19 +20231,19 @@
         <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>81</v>
@@ -20272,7 +20292,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -20293,7 +20313,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -20304,10 +20324,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20333,10 +20353,10 @@
         <v>110</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20366,10 +20386,10 @@
         <v>178</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>81</v>
@@ -20387,7 +20407,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20408,7 +20428,7 @@
         <v>81</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>81</v>
@@ -20419,10 +20439,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20445,13 +20465,13 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20459,7 +20479,7 @@
         <v>81</v>
       </c>
       <c r="Q146" t="s" s="2">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="R146" t="s" s="2">
         <v>81</v>
@@ -20504,7 +20524,7 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20525,7 +20545,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -20536,10 +20556,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20562,13 +20582,13 @@
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20619,7 +20639,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20640,7 +20660,7 @@
         <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>81</v>
@@ -20651,10 +20671,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20677,13 +20697,13 @@
         <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20734,7 +20754,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20755,7 +20775,7 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
@@ -20766,10 +20786,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20792,13 +20812,13 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20849,7 +20869,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20870,7 +20890,7 @@
         <v>81</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
@@ -20881,10 +20901,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20910,10 +20930,10 @@
         <v>110</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20943,10 +20963,10 @@
         <v>178</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>81</v>
@@ -20964,7 +20984,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20985,7 +21005,7 @@
         <v>81</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
@@ -20996,10 +21016,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21025,13 +21045,13 @@
         <v>110</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -21061,7 +21081,7 @@
       </c>
       <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>81</v>
@@ -21079,7 +21099,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -21111,10 +21131,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21137,16 +21157,16 @@
         <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21196,7 +21216,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -21228,10 +21248,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21257,16 +21277,16 @@
         <v>110</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
@@ -21294,10 +21314,10 @@
         <v>178</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>81</v>
@@ -21315,7 +21335,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21336,7 +21356,7 @@
         <v>81</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
@@ -21347,10 +21367,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21373,13 +21393,13 @@
         <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -21430,7 +21450,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21451,7 +21471,7 @@
         <v>81</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>81</v>
@@ -21462,10 +21482,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21491,13 +21511,13 @@
         <v>186</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21526,10 +21546,10 @@
         <v>114</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>81</v>
@@ -21547,7 +21567,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21568,7 +21588,7 @@
         <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
@@ -21579,10 +21599,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21605,16 +21625,16 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21643,10 +21663,10 @@
         <v>190</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>81</v>
@@ -21664,7 +21684,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21685,21 +21705,21 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21725,16 +21745,16 @@
         <v>186</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21763,7 +21783,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>81</v>
@@ -21781,7 +21801,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21802,21 +21822,21 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21842,14 +21862,14 @@
         <v>186</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>81</v>
@@ -21878,7 +21898,7 @@
       </c>
       <c r="Y158" s="2"/>
       <c r="Z158" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>81</v>
@@ -21896,7 +21916,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21917,21 +21937,21 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21957,16 +21977,16 @@
         <v>186</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -21994,10 +22014,10 @@
         <v>190</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>81</v>
@@ -22015,7 +22035,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -22036,21 +22056,21 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22073,13 +22093,13 @@
         <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -22130,7 +22150,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22157,15 +22177,15 @@
         <v>81</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>806</v>
+        <v>811</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22277,10 +22297,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22394,10 +22414,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22423,14 +22443,14 @@
         <v>186</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22458,10 +22478,10 @@
         <v>190</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>81</v>
@@ -22479,7 +22499,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22506,15 +22526,15 @@
         <v>81</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>816</v>
+        <v>821</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22537,19 +22557,19 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22586,7 +22606,7 @@
         <v>81</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AC164" s="2"/>
       <c r="AD164" t="s" s="2">
@@ -22596,7 +22616,7 @@
         <v>139</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22617,24 +22637,24 @@
         <v>81</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>824</v>
+        <v>829</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>81</v>
@@ -22656,19 +22676,19 @@
         <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="O165" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="L165" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22717,7 +22737,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22738,21 +22758,21 @@
         <v>81</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>824</v>
+        <v>829</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22864,10 +22884,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22981,10 +23001,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23007,16 +23027,16 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23066,7 +23086,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -23087,21 +23107,21 @@
         <v>81</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>840</v>
+        <v>845</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23124,16 +23144,16 @@
         <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -23183,7 +23203,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -23204,21 +23224,21 @@
         <v>81</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>847</v>
+        <v>852</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23241,19 +23261,19 @@
         <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>81</v>
@@ -23290,7 +23310,7 @@
         <v>81</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AC170" s="2"/>
       <c r="AD170" t="s" s="2">
@@ -23300,7 +23320,7 @@
         <v>139</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -23321,24 +23341,24 @@
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="D171" t="s" s="2">
         <v>81</v>
@@ -23360,19 +23380,19 @@
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>81</v>
@@ -23421,7 +23441,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -23442,21 +23462,21 @@
         <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23568,10 +23588,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23685,10 +23705,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23711,16 +23731,16 @@
         <v>91</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23770,7 +23790,7 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23791,21 +23811,21 @@
         <v>81</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>840</v>
+        <v>845</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23828,16 +23848,16 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23887,7 +23907,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23908,21 +23928,21 @@
         <v>81</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>847</v>
+        <v>852</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23945,19 +23965,19 @@
         <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -24006,7 +24026,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -24027,21 +24047,21 @@
         <v>81</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24153,10 +24173,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24270,10 +24290,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24296,13 +24316,13 @@
         <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -24353,7 +24373,7 @@
         <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -24374,7 +24394,7 @@
         <v>81</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>81</v>
@@ -24385,10 +24405,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24411,13 +24431,13 @@
         <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -24468,7 +24488,7 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24489,7 +24509,7 @@
         <v>81</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>81</v>
@@ -24500,10 +24520,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24526,19 +24546,19 @@
         <v>91</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>81</v>
@@ -24587,7 +24607,7 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24608,7 +24628,7 @@
         <v>81</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>81</v>
@@ -24619,10 +24639,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24645,17 +24665,17 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" t="s" s="2">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>81</v>
@@ -24704,7 +24724,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24725,7 +24745,7 @@
         <v>81</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
@@ -24736,10 +24756,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24762,13 +24782,13 @@
         <v>81</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24819,7 +24839,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24837,10 +24857,10 @@
         <v>81</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
@@ -24851,10 +24871,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24966,10 +24986,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24995,7 +25015,7 @@
         <v>135</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="M185" t="s" s="2">
         <v>137</v>
@@ -25079,13 +25099,13 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>81</v>
@@ -25107,13 +25127,13 @@
         <v>81</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25196,14 +25216,14 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -25225,10 +25245,10 @@
         <v>135</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N187" t="s" s="2">
         <v>152</v>
@@ -25283,7 +25303,7 @@
         <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25315,10 +25335,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25341,16 +25361,16 @@
         <v>81</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25400,7 +25420,7 @@
         <v>81</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25421,7 +25441,7 @@
         <v>81</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>81</v>
@@ -25432,10 +25452,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25547,10 +25567,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25664,14 +25684,14 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
@@ -25693,10 +25713,10 @@
         <v>135</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N191" t="s" s="2">
         <v>152</v>
@@ -25751,7 +25771,7 @@
         <v>81</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25783,10 +25803,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25809,13 +25829,13 @@
         <v>81</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25866,7 +25886,7 @@
         <v>81</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -25887,7 +25907,7 @@
         <v>81</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>81</v>
@@ -25898,10 +25918,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25924,13 +25944,13 @@
         <v>81</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -25981,7 +26001,7 @@
         <v>81</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -26002,7 +26022,7 @@
         <v>81</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>81</v>
@@ -26013,10 +26033,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26039,13 +26059,13 @@
         <v>81</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -26096,7 +26116,7 @@
         <v>81</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -26117,7 +26137,7 @@
         <v>81</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>81</v>
@@ -26128,10 +26148,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26154,19 +26174,19 @@
         <v>81</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>81</v>
@@ -26215,7 +26235,7 @@
         <v>81</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -26233,10 +26253,10 @@
         <v>81</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="AN195" t="s" s="2">
         <v>81</v>
@@ -26247,10 +26267,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26273,16 +26293,16 @@
         <v>81</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -26332,7 +26352,7 @@
         <v>81</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -26350,24 +26370,24 @@
         <v>81</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>950</v>
+        <v>955</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26390,13 +26410,13 @@
         <v>81</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26447,7 +26467,7 @@
         <v>81</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -26465,24 +26485,24 @@
         <v>81</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="AN197" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>956</v>
+        <v>961</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26505,16 +26525,16 @@
         <v>81</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26564,7 +26584,7 @@
         <v>81</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26582,10 +26602,10 @@
         <v>81</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="AN198" t="s" s="2">
         <v>81</v>
@@ -26596,10 +26616,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26622,13 +26642,13 @@
         <v>81</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26679,7 +26699,7 @@
         <v>81</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26700,7 +26720,7 @@
         <v>81</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="AN199" t="s" s="2">
         <v>494</v>
@@ -26711,10 +26731,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26737,13 +26757,13 @@
         <v>81</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -26794,7 +26814,7 @@
         <v>81</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26812,10 +26832,10 @@
         <v>81</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="AN200" t="s" s="2">
         <v>81</v>
@@ -26826,10 +26846,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26941,10 +26961,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27058,14 +27078,14 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
@@ -27087,10 +27107,10 @@
         <v>135</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N203" t="s" s="2">
         <v>152</v>
@@ -27145,7 +27165,7 @@
         <v>81</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -27177,10 +27197,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27203,16 +27223,16 @@
         <v>81</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -27241,16 +27261,16 @@
         <v>190</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AC204" s="2"/>
       <c r="AD204" t="s" s="2">
@@ -27260,7 +27280,7 @@
         <v>139</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>90</v>
@@ -27278,27 +27298,27 @@
         <v>81</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>983</v>
+        <v>988</v>
       </c>
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>81</v>
@@ -27323,13 +27343,13 @@
         <v>186</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27359,7 +27379,7 @@
       </c>
       <c r="Y205" s="2"/>
       <c r="Z205" t="s" s="2">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>81</v>
@@ -27377,7 +27397,7 @@
         <v>81</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>90</v>
@@ -27395,24 +27415,24 @@
         <v>81</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>983</v>
+        <v>988</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27438,10 +27458,10 @@
         <v>186</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -27471,10 +27491,10 @@
         <v>190</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>81</v>
@@ -27492,7 +27512,7 @@
         <v>81</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27510,24 +27530,24 @@
         <v>81</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="AN206" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27553,10 +27573,10 @@
         <v>334</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -27607,7 +27627,7 @@
         <v>81</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27622,13 +27642,13 @@
         <v>102</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="AN207" t="s" s="2">
         <v>81</v>
@@ -27639,14 +27659,14 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
@@ -27665,16 +27685,16 @@
         <v>81</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27724,7 +27744,7 @@
         <v>81</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27745,7 +27765,7 @@
         <v>81</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="AN208" t="s" s="2">
         <v>81</v>
@@ -27756,10 +27776,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27782,16 +27802,16 @@
         <v>81</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -27841,7 +27861,7 @@
         <v>81</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27856,13 +27876,13 @@
         <v>102</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>81</v>
